--- a/main/ig/mappingPatientCDAFHIR.xlsx
+++ b/main/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T15:44:19+00:00</t>
+    <t>2025-08-01T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPatientCDAFHIR.xlsx
+++ b/main/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T08:11:50+00:00</t>
+    <t>2025-08-22T10:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPatientCDAFHIR.xlsx
+++ b/main/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T10:16:53+00:00</t>
+    <t>2025-08-25T15:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPatientCDAFHIR.xlsx
+++ b/main/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:42:10+00:00</t>
+    <t>2025-10-02T14:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPatientCDAFHIR.xlsx
+++ b/main/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T14:05:03+00:00</t>
+    <t>2025-10-02T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPatientCDAFHIR.xlsx
+++ b/main/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T15:16:38+00:00</t>
+    <t>2025-10-13T15:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPatientCDAFHIR.xlsx
+++ b/main/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T15:21:05+00:00</t>
+    <t>2025-10-20T17:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPatientCDAFHIR.xlsx
+++ b/main/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-20T17:15:49+00:00</t>
+    <t>2025-10-21T08:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPatientCDAFHIR.xlsx
+++ b/main/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T08:14:34+00:00</t>
+    <t>2025-10-21T15:23:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPatientCDAFHIR.xlsx
+++ b/main/ig/mappingPatientCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="130">
   <si>
     <t>Property</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T15:23:03+00:00</t>
+    <t>2025-10-21T16:49:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,205 +105,208 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Patient</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-record-target</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-record-target</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager</t>
+  </si>
+  <si>
+    <t>equivalent</t>
+  </si>
+  <si>
+    <t>recordTarget</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.identifiantPatient</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.id</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.adresse</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.addr</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.coordonneesTelecom</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.telecom</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.nomsPrenomsPatient</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.name</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.nomsPrenomsPatient.nom</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.name.family</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.nomsPrenomsPatient.nom.nomNaissance</t>
+  </si>
+  <si>
+    <t>PrecordTarget.patientRole.patient.name.family@qualifier='BR'</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.nomsPrenomsPatient.nom.nomUtilise</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.name.family@qualifier='CL'</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.nomsPrenomsPatient.prenom</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.name.given</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.nomsPrenomsPatient.prenom.listePrenoms</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.nomsPrenomsPatient.prenom.premierPrenom</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.name.given@qualifier='BR'</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.nomsPrenomsPatient.prenom.prenomUtilise</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.name.given@qualifier='CL'</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.sexe</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.administrativeGenderCode</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.dateNaissance</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.birthTime</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.indicateurDeces</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.sdtc:deceasedInd</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.dateDeces</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.sdtc:deceasedTime</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.grossesseMultiple</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.sdtc:multipleBirthInd</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.numeroOrdreNaissance</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.sdtc:multipleBirthOrderNumber</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.representantPatient</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.guardian</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.representantPatient.adresse</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.guardian.addr</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.representantPatient.coordonneesTelecom</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.guardian.telecom</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenomsRepresentantPatient</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.guardian.guardianPerson.name</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenomsRepresentantPatient.nom</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.guardian.guardianPerson.family</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenomsRepresentantPatient.prenom</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.guardian.guardianPerson.given</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.representantPatient.structureRepresentantPatient</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.guardian.guardianOrganization</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.representantPatient.structureRepresentantPatient.identifiant</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.guardian.guardianOrganization.id</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.representantPatient.structureRepresentantPatient.nom</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.guardian.guardianOrganization.name</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.lieuNaissance</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.birthPlace</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.lieuNaissance.nomLieuNaissance</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.birthPlace.place.name</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.lieuNaissance.adresseLieuNaissance</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.birthPlace.place.addr</t>
+  </si>
+  <si>
+    <t>FRLMPatientUsager.personnePhysique.lieuNaissance.adresseLieuNaissance.codeOfficielGeographiqueLieuNaissance</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.birthPlace.place.addr.county</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-fhir-document</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole</t>
   </si>
   <si>
     <t>Patient</t>
-  </si>
-  <si>
-    <t>equivalent</t>
-  </si>
-  <si>
-    <t>recordTarget</t>
-  </si>
-  <si>
-    <t>Patient.identifiantPatient</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.id</t>
-  </si>
-  <si>
-    <t>Patient.adresse</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.addr</t>
-  </si>
-  <si>
-    <t>Patient.coordonneesTelecom</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.telecom</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.nomsPrenomsPatient</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.name</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.nomsPrenomsPatient.nom</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.name.family</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.nomsPrenomsPatient.nom.nomNaissance</t>
-  </si>
-  <si>
-    <t>PrecordTarget.patientRole.patient.name.family@qualifier='BR'</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.nomsPrenomsPatient.nom.nomUtilise</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.name.family@qualifier='CL'</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.nomsPrenomsPatient.prenom</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.name.given</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.nomsPrenomsPatient.prenom.listePrenoms</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.nomsPrenomsPatient.prenom.premierPrenom</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.name.given@qualifier='BR'</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.nomsPrenomsPatient.prenom.prenomUtilise</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.name.given@qualifier='CL'</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.sexe</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.administrativeGenderCode</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.dateNaissance</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.birthTime</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.indicateurDeces</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.sdtc:deceasedInd</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.dateDeces</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.sdtc:deceasedTime</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.grossesseMultiple</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.sdtc:multipleBirthInd</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.numeroOrdreNaissance</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.sdtc:multipleBirthOrderNumber</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.guardian</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.adresse</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.guardian.addr</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.coordonneesTelecom</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.guardian.telecom</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenomsRepresentantPatient</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.guardian.guardianPerson.name</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenomsRepresentantPatient.nom</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.guardian.guardianPerson.family</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenomsRepresentantPatient.prenom</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.guardian.guardianPerson.given</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.structureRepresentantPatient</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.guardian.guardianOrganization</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.structureRepresentantPatient.identifiant</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.guardian.guardianOrganization.id</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.structureRepresentantPatient.nom</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.guardian.guardianOrganization.name</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.lieuNaissance</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.birthPlace</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.lieuNaissance.nomLieuNaissance</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.birthPlace.place.name</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.lieuNaissance.adresseLieuNaissance</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.birthPlace.place.addr</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.lieuNaissance.adresseLieuNaissance.codeOfficielGeographiqueLieuNaissance</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.birthPlace.place.addr.county</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-fhir-document</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole</t>
   </si>
   <si>
     <t>Patient.identifier</t>
@@ -1151,7 +1154,7 @@
         <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -1164,7 +1167,7 @@
         <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E4" s="2"/>
     </row>
@@ -1177,7 +1180,7 @@
         <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -1190,7 +1193,7 @@
         <v>33</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -1203,7 +1206,7 @@
         <v>33</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -1216,20 +1219,20 @@
         <v>33</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E9" s="2"/>
     </row>
@@ -1242,7 +1245,7 @@
         <v>33</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E10" s="2"/>
     </row>
@@ -1255,7 +1258,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E11" s="2"/>
     </row>
@@ -1268,7 +1271,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E12" s="2"/>
     </row>
@@ -1281,7 +1284,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E13" s="2"/>
     </row>
@@ -1294,7 +1297,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E14" s="2"/>
     </row>
@@ -1307,7 +1310,7 @@
         <v>33</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E15" s="2"/>
     </row>
@@ -1320,7 +1323,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E16" s="2"/>
     </row>
@@ -1333,7 +1336,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E17" s="2"/>
     </row>
@@ -1346,7 +1349,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E18" s="2"/>
     </row>
@@ -1359,7 +1362,7 @@
         <v>33</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E19" s="2"/>
     </row>
@@ -1372,7 +1375,7 @@
         <v>33</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E20" s="2"/>
     </row>
@@ -1385,7 +1388,7 @@
         <v>33</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E21" s="2"/>
     </row>
@@ -1398,7 +1401,7 @@
         <v>33</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E22" s="2"/>
     </row>
@@ -1411,7 +1414,7 @@
         <v>33</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E23" s="2"/>
     </row>
@@ -1424,7 +1427,7 @@
         <v>33</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E24" s="2"/>
     </row>
@@ -1437,7 +1440,7 @@
         <v>33</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E25" s="2"/>
     </row>
@@ -1450,7 +1453,7 @@
         <v>33</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E26" s="2"/>
     </row>
@@ -1463,7 +1466,7 @@
         <v>33</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E27" s="2"/>
     </row>
@@ -1476,7 +1479,7 @@
         <v>33</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E28" s="2"/>
     </row>
@@ -1489,7 +1492,7 @@
         <v>33</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E29" s="2"/>
     </row>
@@ -1502,20 +1505,20 @@
         <v>33</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E31" s="2"/>
     </row>
@@ -1528,20 +1531,20 @@
         <v>33</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E33" s="2"/>
     </row>

--- a/main/ig/mappingPatientCDAFHIR.xlsx
+++ b/main/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T16:49:23+00:00</t>
+    <t>2025-10-21T17:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPatientCDAFHIR.xlsx
+++ b/main/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T17:18:21+00:00</t>
+    <t>2025-10-22T08:56:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
